--- a/docs/Lab2/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab2/Lab02_BBT_TCs_Form.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" state="visible" r:id="rId3"/>
@@ -20,40 +20,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="D22" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Author:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">max = 
-Current Year</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -114,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="126">
   <si>
     <t xml:space="preserve">VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -496,6 +462,29 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F01.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> adăugarea unui pridus  nou (id, nume, pret, categorie, tip);</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">BVA Condition</t>
   </si>
   <si>
@@ -517,139 +506,112 @@
     <t xml:space="preserve">Executable</t>
   </si>
   <si>
-    <t xml:space="preserve">titlu is String, length in [1,255]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01. titlu = "", length = 0</t>
+    <t xml:space="preserve">nume is String, length &gt; 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. nume = "", length = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tip</t>
   </si>
   <si>
     <t xml:space="preserve">expected result</t>
   </si>
   <si>
-    <t xml:space="preserve">02. titlu = ?, length = -1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC3_EC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03. titlu = "M", length = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04. titlu = "M…123", length = 255</t>
+    <t xml:space="preserve">02. nume = "M", length = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error Thrown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“M”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record Added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pret &gt;= 0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03. pret = -1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04. pret = 0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBT TCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final        TC No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Req. ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECP TCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BVA TCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actual result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC1_ECP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director1, Director2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC3_ECP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error message-Empty movie title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC5_ECP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC3_BVA</t>
   </si>
   <si>
     <t xml:space="preserve">"M"</t>
   </si>
   <si>
-    <t xml:space="preserve"> Director1, Director 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05. titlu = "M…12", length = 254</t>
+    <t xml:space="preserve">TC4_BVA</t>
   </si>
   <si>
     <t xml:space="preserve">"M…123"</t>
   </si>
   <si>
-    <t xml:space="preserve">06. titlu = "M…1234", length = 256</t>
+    <t xml:space="preserve">TC5_BVA</t>
   </si>
   <si>
     <t xml:space="preserve">"M…12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regizor is String, length in [1,255]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07. regizor = "", length = 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"M…1234"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08. regizor = ?, length = -1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09. regizor = "D", length = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. regizor = "D…123", length = 255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. regizor = "D…12", length = 254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12. regizor = "D…1234", length = 256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">an aparitie &gt;1900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. an = 1960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14. an = 1959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15. an = 1961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16. an = max - 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17. an = max + 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18. an = max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BBT TCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final        TC No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Req. ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECP TCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BVA TCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">actual result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC1_ECP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director1, Director2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC3_ECP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error message-Empty movie title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC5_ECP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC3_BVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC4_BVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC5_BVA</t>
   </si>
   <si>
     <t xml:space="preserve">Statistics</t>
@@ -734,10 +696,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -889,21 +852,16 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -956,6 +914,18 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -1150,340 +1120,372 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="92">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="7" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="7" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1743,212 +1745,212 @@
   <dimension ref="A1:O26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="32.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="32.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="H1" s="2" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="H1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="5" t="n">
         <v>232</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="5" t="n">
         <v>232</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5"/>
-      <c r="H6" s="4" t="s">
+      <c r="B6" s="6"/>
+      <c r="H6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="5" t="n">
         <v>232</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11" t="s">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="12"/>
+      <c r="C26" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1975,530 +1977,530 @@
   <dimension ref="B1:Q22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="25.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="29.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="25.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="29.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="G5" s="15" t="s">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="G5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16" t="s">
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="Q6" s="16"/>
+      <c r="Q6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16" t="s">
+      <c r="E7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16" t="s">
+      <c r="O7" s="17"/>
+      <c r="P7" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="Q7" s="16"/>
+      <c r="Q7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18" t="s">
+      <c r="C8" s="20"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="O8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="P8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q8" s="3"/>
+      <c r="Q8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="G9" s="16" t="n">
+      <c r="E9" s="19"/>
+      <c r="G9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" s="4" t="s">
+      <c r="H9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="M9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="O9" s="3" t="s">
+      <c r="M9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="O9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q9" s="3"/>
+      <c r="P9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="J10" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="21" t="n">
+      <c r="K10" s="22" t="n">
         <v>2012</v>
       </c>
-      <c r="L10" s="22" t="s">
+      <c r="L10" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="M10" s="22" t="s">
+      <c r="M10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N10" s="23" t="s">
+      <c r="N10" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23" t="s">
+      <c r="O10" s="24"/>
+      <c r="P10" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="Q10" s="23"/>
+      <c r="Q10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="G11" s="20" t="n">
+      <c r="E11" s="19"/>
+      <c r="G11" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="22" t="s">
+      <c r="H11" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="L11" s="22" t="s">
+      <c r="L11" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="M11" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="N11" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q11" s="23"/>
+      <c r="M11" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18" t="s">
+      <c r="C12" s="20"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="I12" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="K12" s="25" t="s">
+      <c r="K12" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="L12" s="25" t="s">
+      <c r="L12" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="M12" s="25" t="s">
+      <c r="M12" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="N12" s="25" t="s">
+      <c r="N12" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="O12" s="25"/>
-      <c r="P12" s="26" t="s">
+      <c r="O12" s="26"/>
+      <c r="P12" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="Q12" s="26"/>
+      <c r="Q12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="G13" s="24" t="n">
+      <c r="E13" s="19"/>
+      <c r="G13" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="K13" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" s="25" t="s">
+      <c r="H13" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="M13" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="N13" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="O13" s="26"/>
-      <c r="P13" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q13" s="26"/>
+      <c r="M13" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q13" s="27"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18" t="s">
+      <c r="C14" s="20"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H14" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="K14" s="21" t="s">
+      <c r="K14" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="L14" s="21" t="s">
+      <c r="L14" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="21" t="s">
+      <c r="M14" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="N14" s="28" t="s">
+      <c r="N14" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="O14" s="28"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="30"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="G15" s="27" t="n">
+      <c r="C15" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="G15" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
+      <c r="H15" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="30"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
+      <c r="C17" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="30"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="29"/>
+      <c r="C19" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="41">
@@ -2560,716 +2562,603 @@
     <tabColor rgb="FFFCD5B5"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:R30"/>
+  <dimension ref="B1:Q30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="23.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="18.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="7.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="23.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="33"/>
+      <c r="G5" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="34"/>
+      <c r="G6" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q6" s="35"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="N7" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="O7" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q7" s="17"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="19"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="M8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="O8" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q8" s="38"/>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="19"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="5"/>
+      <c r="G9" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="M9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="O9" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="P9" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q9" s="43"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="19"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="5"/>
+      <c r="G10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="M10" s="40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="O10" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="P10" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q10" s="38"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="19"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="5"/>
+      <c r="G11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="M11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="O11" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="P11" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q11" s="38"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="19"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="5"/>
+      <c r="G12" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="37"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="48"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="19"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="37"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="19"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="5"/>
+      <c r="G15" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="37"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="19"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="5"/>
+      <c r="G16" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="37"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="19"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="5"/>
+      <c r="G17" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" s="37"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="19"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="5"/>
+      <c r="G18" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H18" s="37"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="19"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="5"/>
+      <c r="G19" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" s="37"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="19"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="5"/>
+      <c r="G20" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" s="37"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="19"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="5"/>
+      <c r="G21" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" s="37"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="19"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="5"/>
+      <c r="G22" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" s="37"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="19"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="5"/>
+      <c r="G23" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H23" s="37"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="19"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="5"/>
+      <c r="G24" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="32"/>
-      <c r="G5" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="33"/>
-      <c r="G6" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="K6" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="R6" s="34"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="O7" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="P7" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q7" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="R7" s="16"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="18"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="J8" s="37"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="18"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="M9" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="P9" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q9" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="R9" s="26"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="18"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="L10" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="M10" s="38" t="n">
-        <v>2010</v>
-      </c>
-      <c r="N10" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="O10" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="P10" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q10" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="R10" s="37"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="18"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="L11" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="M11" s="38" t="n">
-        <v>2010</v>
-      </c>
-      <c r="N11" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="O11" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="P11" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q11" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="R11" s="37"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="18"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="L12" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="M12" s="38" t="n">
-        <v>2010</v>
-      </c>
-      <c r="N12" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="O12" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="P12" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q12" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="R12" s="37"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="L13" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="M13" s="21" t="n">
-        <v>2010</v>
-      </c>
-      <c r="N13" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="O13" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="P13" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q13" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="R13" s="26"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="38"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="H15" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="I15" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="H16" s="36"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="H17" s="36"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="H18" s="36"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="H19" s="36"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="18"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="18"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="H21" s="36"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="18"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="18"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="H23" s="36"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="37"/>
-      <c r="R23" s="37"/>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="18"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="H24" s="36"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
       <c r="P24" s="38"/>
-      <c r="Q24" s="37"/>
-      <c r="R24" s="37"/>
+      <c r="Q24" s="38"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" s="16" t="n">
+      <c r="B25" s="19"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="5"/>
+      <c r="G25" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="H25" s="36"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="39"/>
       <c r="P25" s="38"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="Q25" s="38"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="18"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="18"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="18"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="42"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="43"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="5"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="50"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="51"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="18"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="44"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="45"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="5"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="52"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="53"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="18"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="40">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:R5"/>
+    <mergeCell ref="G5:Q5"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P6:Q6"/>
     <mergeCell ref="B7:B12"/>
     <mergeCell ref="C7:C12"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
     <mergeCell ref="B13:B18"/>
     <mergeCell ref="C13:C18"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
     <mergeCell ref="B19:B24"/>
     <mergeCell ref="C19:C24"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P24:Q24"/>
     <mergeCell ref="B25:B30"/>
     <mergeCell ref="C25:C30"/>
-    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="P25:Q25"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="I28:M28"/>
     <mergeCell ref="I29:M29"/>
@@ -3281,7 +3170,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3294,569 +3182,569 @@
   <dimension ref="B1:P21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="10.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="30.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="10.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
+      <c r="B3" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="47" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="E4" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="F4" s="16" t="s">
+      <c r="B4" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="16"/>
+      <c r="N4" s="17"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="50" t="s">
+      <c r="G5" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="50" t="s">
+      <c r="H5" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="50" t="s">
+      <c r="I5" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="50" t="s">
+      <c r="J5" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="50" t="s">
+      <c r="K5" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50" t="s">
+      <c r="L5" s="58"/>
+      <c r="M5" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="50" t="s">
-        <v>112</v>
+      <c r="N5" s="58" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="51" t="n">
+      <c r="B6" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="51" t="s">
+      <c r="C6" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="F6" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="54" t="s">
-        <v>115</v>
-      </c>
-      <c r="H6" s="54" t="n">
+      <c r="G6" s="62" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="62" t="n">
         <v>2010</v>
       </c>
-      <c r="I6" s="54" t="s">
+      <c r="I6" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="55" t="s">
+      <c r="J6" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="55" t="s">
+      <c r="L6" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="54" t="s">
+      <c r="M6" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="51" t="s">
+      <c r="N6" s="59" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="56" t="n">
+      <c r="B7" s="64" t="n">
         <f aca="false">B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="56" t="s">
+      <c r="C7" s="60"/>
+      <c r="D7" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="58" t="s">
-        <v>115</v>
-      </c>
-      <c r="H7" s="58" t="n">
+      <c r="G7" s="66" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="66" t="n">
         <v>2010</v>
       </c>
-      <c r="I7" s="58" t="s">
+      <c r="I7" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="59" t="s">
+      <c r="J7" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="K7" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="59"/>
-      <c r="M7" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="N7" s="56" t="s">
+      <c r="L7" s="67"/>
+      <c r="M7" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="N7" s="64" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="56" t="n">
+      <c r="B8" s="64" t="n">
         <f aca="false">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="56" t="s">
+      <c r="C8" s="60"/>
+      <c r="D8" s="65" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="60" t="s">
+      <c r="F8" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="60" t="s">
-        <v>115</v>
-      </c>
-      <c r="H8" s="60" t="s">
+      <c r="G8" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="60" t="s">
+      <c r="I8" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="60" t="s">
-        <v>87</v>
-      </c>
-      <c r="K8" s="60" t="s">
+      <c r="J8" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="K8" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60" t="s">
+      <c r="L8" s="68"/>
+      <c r="M8" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="N8" s="56" t="s">
+      <c r="N8" s="64" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="56" t="n">
+      <c r="B9" s="64" t="n">
         <f aca="false">B8+1</f>
         <v>4</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="56" t="s">
+      <c r="C9" s="60"/>
+      <c r="D9" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="56" t="s">
+      <c r="F9" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" s="56"/>
-      <c r="M9" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="N9" s="56" t="s">
+      <c r="J9" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="64" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="56" t="n">
+      <c r="B10" s="64" t="n">
         <f aca="false">B9+1</f>
         <v>5</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="57" t="s">
+      <c r="C10" s="60"/>
+      <c r="D10" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="61" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" s="62" t="s">
-        <v>115</v>
-      </c>
-      <c r="H10" s="62" t="n">
+      <c r="E10" s="64" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="70" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="70" t="n">
         <v>2010</v>
       </c>
-      <c r="I10" s="62" t="s">
+      <c r="I10" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="63" t="s">
+      <c r="J10" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="K10" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="63"/>
-      <c r="M10" s="60" t="s">
+      <c r="L10" s="71"/>
+      <c r="M10" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="N10" s="56" t="s">
+      <c r="N10" s="64" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="56" t="n">
+      <c r="B11" s="64" t="n">
         <f aca="false">B10+1</f>
         <v>6</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="57" t="s">
+      <c r="C11" s="60"/>
+      <c r="D11" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="F11" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="62" t="s">
-        <v>115</v>
-      </c>
-      <c r="H11" s="62" t="n">
+      <c r="E11" s="64" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="70" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="70" t="n">
         <v>2010</v>
       </c>
-      <c r="I11" s="62" t="s">
+      <c r="I11" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="63" t="s">
+      <c r="J11" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="K11" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="63"/>
-      <c r="M11" s="64" t="s">
+      <c r="L11" s="71"/>
+      <c r="M11" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="N11" s="56" t="s">
+      <c r="N11" s="64" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="56" t="n">
+      <c r="B12" s="64" t="n">
         <f aca="false">B11+1</f>
         <v>7</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="57" t="s">
+      <c r="C12" s="60"/>
+      <c r="D12" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="56" t="s">
-        <v>121</v>
-      </c>
-      <c r="F12" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="G12" s="62" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="62" t="n">
+      <c r="E12" s="64" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="70" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="70" t="n">
         <v>2010</v>
       </c>
-      <c r="I12" s="62" t="s">
+      <c r="I12" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" s="63" t="s">
+      <c r="J12" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="K12" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="63"/>
-      <c r="M12" s="64" t="s">
+      <c r="L12" s="71"/>
+      <c r="M12" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="56" t="s">
+      <c r="N12" s="64" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="65" t="n">
+      <c r="B13" s="73" t="n">
         <f aca="false">B12+1</f>
         <v>8</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="65" t="s">
+      <c r="C13" s="60"/>
+      <c r="D13" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="65" t="s">
+      <c r="I13" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="K13" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="N13" s="65" t="s">
+      <c r="J13" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="73"/>
+      <c r="M13" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="73" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="66"/>
-      <c r="M14" s="66"/>
-      <c r="N14" s="66"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="74"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="74" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="74"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="76"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M16" s="76"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="78" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="79" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="78" t="s">
+        <v>117</v>
+      </c>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78" t="s">
+        <v>118</v>
+      </c>
+      <c r="N17" s="78"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="80" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="82" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="66"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="69"/>
-      <c r="M15" s="68"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M16" s="68"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="70" t="s">
+      <c r="G18" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="71" t="s">
+      <c r="H18" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="H17" s="70" t="s">
+      <c r="I18" s="81"/>
+      <c r="J18" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="L18" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="M18" s="84" t="s">
+        <v>124</v>
+      </c>
+      <c r="N18" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="O18" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="P18" s="82" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="80"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="82"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="82"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="86" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="88"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="I17" s="70"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="70" t="s">
-        <v>126</v>
-      </c>
-      <c r="N17" s="70"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="70"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="72" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="73" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="F18" s="74" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="H18" s="73" t="s">
-        <v>132</v>
-      </c>
-      <c r="I18" s="73"/>
-      <c r="J18" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="L18" s="74" t="s">
-        <v>129</v>
-      </c>
-      <c r="M18" s="76" t="s">
-        <v>132</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="P18" s="74" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="72"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="75"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="74"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="77" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="78" t="n">
-        <v>8</v>
-      </c>
-      <c r="D20" s="79" t="n">
+      <c r="I20" s="90"/>
+      <c r="J20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="91" t="s">
+        <v>125</v>
+      </c>
+      <c r="N20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="79" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="80"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="82" t="s">
-        <v>133</v>
-      </c>
-      <c r="I20" s="82"/>
-      <c r="J20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" s="79" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" s="80" t="n">
+      <c r="O20" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="83" t="s">
-        <v>133</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" s="79" t="n">
-        <v>5</v>
-      </c>
-      <c r="P20" s="80" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M21" s="32"/>
+      <c r="M21" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="36">

--- a/docs/Lab2/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab2/Lab02_BBT_TCs_Form.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="106">
   <si>
     <t xml:space="preserve">VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -127,156 +127,10 @@
     <t xml:space="preserve">Informaţiile vor fi preluate din fişiere text.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Evidenţa filmelor din colecţia personală</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">F01.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> adăugarea unui film nou (titlu, regizor, an aparitie, actori, categorie, cuvinte cheie);</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Observații</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">addMovie(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Metoda este definită la nivelul repository, service sau ui.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Se aleg doi parametri ai metodei testate şi se definesc condiţii asupra acestora. Condiţiile (constrângerile) rezultă din specificaţii.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Pentru aceşti parametri se aplică ECP şi BVA. La proiectarea testelor se consideră că parametrii de intrare neinvestigaţi aici au valori valide, adică folosim dummy objects.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Exemplu: Parametrii </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">title</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> şi </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">year</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">; Condiţii pentru aceşti parametri de intrare: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">title</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> este un string cu lungimea validă de la 1 la 255 caractere; </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">year</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> este valid dacă ia valori între 1899 şi 2025.</t>
-    </r>
+    <t xml:space="preserve">1. Evidenţa produselor dintr-un magazin de bauturi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un magazin de bauturi doreste un program pentru gestionarea produselor si comenzilor magazinului</t>
   </si>
   <si>
     <r>
@@ -300,6 +154,24 @@
       </rPr>
       <t xml:space="preserve"> adăugarea unui produs nou (id,nume,pret,categorie,tip);</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Observații</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">addProduct (Int id,String nume,Double pret,CategorieBautura categorie, TipBautura tip);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Metoda este definită la nivelul repository, service sau ui.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Se aleg doi parametri ai metodei testate şi se definesc condiţii asupra acestora. Condiţiile (constrângerile) rezultă din specificaţii.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Pentru aceşti parametri se aplică ECP şi BVA. La proiectarea testelor se consideră că parametrii de intrare neinvestigaţi aici au valori valide, adică folosim dummy objects.</t>
   </si>
   <si>
     <t xml:space="preserve">EC Identification</t>
@@ -607,7 +479,7 @@
     <t xml:space="preserve">Added checks</t>
   </si>
   <si>
-    <t xml:space="preserve">not yet</t>
+    <t xml:space="preserve">tests passed</t>
   </si>
 </sst>
 </file>
@@ -618,7 +490,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -686,23 +558,6 @@
       <color theme="1"/>
       <name val="Courier New"/>
       <family val="3"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <i val="true"/>
-      <sz val="11"/>
-      <color rgb="FF0066CC"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF0066CC"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1014,339 +869,339 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="7" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1374,7 +1229,7 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF0070C0"/>
+      <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFCCC1DA"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
@@ -1383,7 +1238,7 @@
       <rgbColor rgb="FFDBEEF4"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF0070C0"/>
       <rgbColor rgb="FFC6D9F1"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -1606,218 +1461,218 @@
   <dimension ref="A1:O26"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="32.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="32.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="H1" s="2" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="H1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="5" t="n">
         <v>232</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="5" t="n">
         <v>232</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5"/>
-      <c r="H6" s="4" t="s">
+      <c r="B6" s="6"/>
+      <c r="H6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="5" t="n">
         <v>232</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="12"/>
+      <c r="C26" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B24:N24"/>
+    <mergeCell ref="B16:G16"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1838,48 +1693,48 @@
   <dimension ref="B1:P22"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="25.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="8.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="29.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="25.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="17.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="29.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="B3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="G5" s="15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
@@ -1893,25 +1748,25 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="E6" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="G6" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="H6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="I6" s="16" t="s">
         <v>32</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>34</v>
       </c>
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
@@ -1920,7 +1775,7 @@
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
       <c r="P6" s="16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1928,28 +1783,28 @@
         <v>1</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E7" s="18"/>
       <c r="G7" s="17"/>
       <c r="H7" s="16"/>
       <c r="I7" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="L7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="M7" s="16" t="s">
         <v>39</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>41</v>
       </c>
       <c r="N7" s="16"/>
       <c r="O7" s="16"/>
@@ -1962,35 +1817,35 @@
       <c r="C8" s="19"/>
       <c r="D8" s="18"/>
       <c r="E8" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="4" t="s">
+      <c r="J8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="N8" s="20"/>
       <c r="O8" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1998,39 +1853,39 @@
         <v>3</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" s="18"/>
       <c r="G9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="4" t="n">
+      <c r="J9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>45</v>
+      <c r="L9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="N9" s="20"/>
       <c r="O9" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2040,7 +1895,7 @@
       <c r="C10" s="19"/>
       <c r="D10" s="18"/>
       <c r="E10" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G10" s="21" t="n">
         <v>3</v>
@@ -2052,21 +1907,21 @@
         <v>2</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K10" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" s="23" t="s">
         <v>43</v>
-      </c>
-      <c r="L10" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="23" t="s">
-        <v>45</v>
       </c>
       <c r="N10" s="24"/>
       <c r="O10" s="24"/>
       <c r="P10" s="24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2086,21 +1941,21 @@
         <v>3</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K11" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="23" t="s">
         <v>43</v>
-      </c>
-      <c r="L11" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="M11" s="23" t="s">
-        <v>45</v>
       </c>
       <c r="N11" s="24"/>
       <c r="O11" s="24"/>
       <c r="P11" s="24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2162,7 +2017,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
@@ -2200,7 +2055,7 @@
         <v>11</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
@@ -2238,17 +2093,17 @@
         <v>13</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
       <c r="N19" s="20"/>
       <c r="O19" s="20"/>
       <c r="P19" s="30"/>
@@ -2262,8 +2117,8 @@
       <c r="E20" s="18"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="0" t="s">
-        <v>54</v>
+      <c r="D22" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F22" s="31"/>
       <c r="G22" s="31"/>
@@ -2317,51 +2172,51 @@
   <dimension ref="B1:P30"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="23.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16383" style="0" width="11.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="18.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="7.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="23.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16383" style="1" width="11.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="B3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="E5" s="33"/>
       <c r="G5" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
@@ -2375,36 +2230,36 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E6" s="34"/>
       <c r="G6" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="J6" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="I6" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>62</v>
-      </c>
       <c r="K6" s="35" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L6" s="35"/>
       <c r="M6" s="35"/>
       <c r="N6" s="35"/>
       <c r="O6" s="35"/>
       <c r="P6" s="35" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2412,39 +2267,39 @@
         <v>1</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
       <c r="J7" s="16"/>
       <c r="K7" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="N7" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="O7" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="N7" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="O7" s="16" t="s">
-        <v>41</v>
-      </c>
       <c r="P7" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="18"/>
       <c r="C8" s="36"/>
-      <c r="D8" s="4" t="s">
-        <v>66</v>
+      <c r="D8" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>1</v>
@@ -2458,25 +2313,25 @@
         <v>1</v>
       </c>
       <c r="L8" s="39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M8" s="40" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="P8" s="38" t="s">
         <v>68</v>
-      </c>
-      <c r="O8" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="P8" s="38" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18"/>
       <c r="C9" s="36"/>
-      <c r="D9" s="4"/>
+      <c r="D9" s="5"/>
       <c r="G9" s="41" t="n">
         <v>2</v>
       </c>
@@ -2489,25 +2344,25 @@
         <v>1</v>
       </c>
       <c r="L9" s="45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O9" s="39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P9" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="18"/>
       <c r="C10" s="36"/>
-      <c r="D10" s="4"/>
+      <c r="D10" s="5"/>
       <c r="G10" s="16" t="n">
         <v>3</v>
       </c>
@@ -2520,25 +2375,25 @@
         <v>2</v>
       </c>
       <c r="L10" s="39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M10" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="O10" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="P10" s="38" t="s">
         <v>68</v>
-      </c>
-      <c r="O10" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="P10" s="38" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18"/>
       <c r="C11" s="36"/>
-      <c r="D11" s="4"/>
+      <c r="D11" s="5"/>
       <c r="G11" s="16" t="n">
         <v>4</v>
       </c>
@@ -2551,25 +2406,25 @@
         <v>2</v>
       </c>
       <c r="L11" s="39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O11" s="39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P11" s="38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18"/>
       <c r="C12" s="36"/>
-      <c r="D12" s="4"/>
+      <c r="D12" s="5"/>
       <c r="G12" s="16" t="n">
         <v>5</v>
       </c>
@@ -2588,10 +2443,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="G13" s="41" t="n">
         <v>6</v>
@@ -2609,8 +2464,8 @@
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="18"/>
       <c r="C14" s="36"/>
-      <c r="D14" s="4" t="s">
-        <v>75</v>
+      <c r="D14" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="G14" s="16" t="n">
         <v>7</v>
@@ -2628,7 +2483,7 @@
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18"/>
       <c r="C15" s="36"/>
-      <c r="D15" s="4"/>
+      <c r="D15" s="5"/>
       <c r="G15" s="16" t="n">
         <v>8</v>
       </c>
@@ -2645,7 +2500,7 @@
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="18"/>
       <c r="C16" s="36"/>
-      <c r="D16" s="4"/>
+      <c r="D16" s="5"/>
       <c r="G16" s="16" t="n">
         <v>9</v>
       </c>
@@ -2662,7 +2517,7 @@
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18"/>
       <c r="C17" s="36"/>
-      <c r="D17" s="4"/>
+      <c r="D17" s="5"/>
       <c r="G17" s="16" t="n">
         <v>10</v>
       </c>
@@ -2679,7 +2534,7 @@
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18"/>
       <c r="C18" s="36"/>
-      <c r="D18" s="4"/>
+      <c r="D18" s="5"/>
       <c r="G18" s="16" t="n">
         <v>11</v>
       </c>
@@ -2696,7 +2551,7 @@
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="18"/>
       <c r="C19" s="36"/>
-      <c r="D19" s="4"/>
+      <c r="D19" s="5"/>
       <c r="G19" s="16" t="n">
         <v>12</v>
       </c>
@@ -2713,7 +2568,7 @@
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="18"/>
       <c r="C20" s="36"/>
-      <c r="D20" s="4"/>
+      <c r="D20" s="5"/>
       <c r="G20" s="16" t="n">
         <v>13</v>
       </c>
@@ -2730,7 +2585,7 @@
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="18"/>
       <c r="C21" s="36"/>
-      <c r="D21" s="4"/>
+      <c r="D21" s="5"/>
       <c r="G21" s="16" t="n">
         <v>14</v>
       </c>
@@ -2747,7 +2602,7 @@
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="18"/>
       <c r="C22" s="36"/>
-      <c r="D22" s="4"/>
+      <c r="D22" s="5"/>
       <c r="G22" s="16" t="n">
         <v>15</v>
       </c>
@@ -2764,7 +2619,7 @@
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="18"/>
       <c r="C23" s="36"/>
-      <c r="D23" s="4"/>
+      <c r="D23" s="5"/>
       <c r="G23" s="16" t="n">
         <v>16</v>
       </c>
@@ -2781,7 +2636,7 @@
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="18"/>
       <c r="C24" s="36"/>
-      <c r="D24" s="4"/>
+      <c r="D24" s="5"/>
       <c r="G24" s="16" t="n">
         <v>17</v>
       </c>
@@ -2798,7 +2653,7 @@
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="18"/>
       <c r="C25" s="36"/>
-      <c r="D25" s="4"/>
+      <c r="D25" s="5"/>
       <c r="G25" s="16" t="n">
         <v>18</v>
       </c>
@@ -2815,17 +2670,17 @@
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18"/>
       <c r="C26" s="36"/>
-      <c r="D26" s="4"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18"/>
       <c r="C27" s="36"/>
-      <c r="D27" s="4"/>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="18"/>
       <c r="C28" s="36"/>
-      <c r="D28" s="4"/>
+      <c r="D28" s="5"/>
       <c r="G28" s="31"/>
       <c r="H28" s="31"/>
       <c r="I28" s="50"/>
@@ -2838,7 +2693,7 @@
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18"/>
       <c r="C29" s="36"/>
-      <c r="D29" s="4"/>
+      <c r="D29" s="5"/>
       <c r="I29" s="52"/>
       <c r="J29" s="52"/>
       <c r="K29" s="52"/>
@@ -2849,7 +2704,7 @@
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="18"/>
       <c r="C30" s="36"/>
-      <c r="D30" s="4"/>
+      <c r="D30" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -2893,27 +2748,27 @@
   <dimension ref="B1:N21"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="28.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="30.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="28.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="54" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
@@ -2928,26 +2783,26 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="E4" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="58" t="s">
-        <v>80</v>
-      </c>
       <c r="F4" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
       <c r="J4" s="16"/>
       <c r="K4" s="16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L4" s="16"/>
     </row>
@@ -2957,25 +2812,25 @@
       <c r="D5" s="57"/>
       <c r="E5" s="58"/>
       <c r="F5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="I5" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="J5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>41</v>
-      </c>
       <c r="K5" s="58" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L5" s="58" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2983,34 +2838,34 @@
         <v>1</v>
       </c>
       <c r="C6" s="60" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F6" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="L6" s="59" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3020,31 +2875,31 @@
       </c>
       <c r="C7" s="60"/>
       <c r="D7" s="64" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E7" s="63" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F7" s="65" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H7" s="45" t="n">
         <v>-1</v>
       </c>
       <c r="I7" s="45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J7" s="45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K7" s="43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L7" s="63" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3054,31 +2909,31 @@
       </c>
       <c r="C8" s="60"/>
       <c r="D8" s="64" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E8" s="63" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F8" s="65" t="n">
         <v>2</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H8" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="45" t="s">
+      <c r="K8" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="43" t="s">
-        <v>47</v>
-      </c>
       <c r="L8" s="63" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3088,31 +2943,31 @@
       </c>
       <c r="C9" s="60"/>
       <c r="D9" s="64" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" s="63" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F9" s="66" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H9" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="I9" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="45" t="s">
+      <c r="K9" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="43" t="s">
-        <v>47</v>
-      </c>
       <c r="L9" s="63" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3122,31 +2977,31 @@
       </c>
       <c r="C10" s="60"/>
       <c r="D10" s="64" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E10" s="63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F10" s="39" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H10" s="40" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="J10" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="K10" s="38" t="s">
-        <v>70</v>
-      </c>
       <c r="L10" s="63" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3156,31 +3011,31 @@
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="64" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E11" s="63" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F11" s="44" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H11" s="46" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J11" s="39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K11" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L11" s="63" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3190,31 +3045,31 @@
       </c>
       <c r="C12" s="60"/>
       <c r="D12" s="64" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E12" s="63" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F12" s="47" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H12" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="I12" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="J12" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="K12" s="38" t="s">
-        <v>70</v>
-      </c>
       <c r="L12" s="63" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3224,31 +3079,31 @@
       </c>
       <c r="C13" s="60"/>
       <c r="D13" s="57" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E13" s="63" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F13" s="47" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H13" s="40" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L13" s="67" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3266,7 +3121,7 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="68" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C15" s="68"/>
       <c r="D15" s="69"/>
@@ -3283,21 +3138,21 @@
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="71" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
       <c r="G17" s="72" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H17" s="71" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I17" s="71"/>
       <c r="J17" s="71"/>
       <c r="K17" s="71" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L17" s="71"/>
       <c r="M17" s="71"/>
@@ -3305,41 +3160,41 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="73" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C18" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="F18" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="G18" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="F18" s="75" t="s">
+      <c r="H18" s="74" t="s">
         <v>102</v>
-      </c>
-      <c r="G18" s="76" t="s">
-        <v>103</v>
-      </c>
-      <c r="H18" s="74" t="s">
-        <v>104</v>
       </c>
       <c r="I18" s="74"/>
       <c r="J18" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="K18" s="77" t="s">
+        <v>102</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="M18" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="N18" s="75" t="s">
         <v>99</v>
-      </c>
-      <c r="K18" s="77" t="s">
-        <v>104</v>
-      </c>
-      <c r="L18" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="M18" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="N18" s="75" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3359,7 +3214,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="78" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C20" s="79" t="n">
         <v>8</v>
@@ -3371,22 +3226,22 @@
         <v>2</v>
       </c>
       <c r="F20" s="81" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="82" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="83" t="s">
         <v>105</v>
       </c>
-      <c r="G20" s="82" t="s">
-        <v>106</v>
-      </c>
-      <c r="H20" s="83" t="s">
-        <v>107</v>
-      </c>
       <c r="I20" s="83"/>
-      <c r="J20" s="4" t="n">
+      <c r="J20" s="5" t="n">
         <v>2</v>
       </c>
       <c r="K20" s="84" t="s">
-        <v>107</v>
-      </c>
-      <c r="L20" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="L20" s="5" t="n">
         <v>6</v>
       </c>
       <c r="M20" s="80" t="n">
